--- a/data/b2_primavera/B2 Primavera 01-2026.xlsx
+++ b/data/b2_primavera/B2 Primavera 01-2026.xlsx
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>2428.31</v>
+        <v>2320.64</v>
       </c>
     </row>
     <row r="3">
@@ -4990,25 +4990,25 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>57744.53</v>
+        <v>57336.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>14000</v>
+        <v>2047.32</v>
       </c>
     </row>
     <row r="5">
@@ -5017,39 +5017,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3600</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3999.49</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -5062,169 +5062,169 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>973.0599999999999</v>
+        <v>948.0599999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1236.85</v>
+        <v>4463.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46037</v>
+        <v>46034</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>8759.629999999999</v>
+        <v>1230.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46037</v>
+        <v>46034</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1449.86</v>
+        <v>1211.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1722.03</v>
+        <v>10466.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46039</v>
+        <v>46037</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>2700.74</v>
+        <v>1792.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1611.86</v>
+        <v>3920.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46040</v>
+        <v>46042</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>3057.69</v>
+        <v>20094.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46040</v>
+        <v>46044</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>4217.97</v>
+        <v>1150.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46042</v>
+        <v>46046</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>20357.23</v>
+        <v>1030.94</v>
       </c>
     </row>
     <row r="17">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>4362.71</v>
+        <v>4374.82</v>
       </c>
     </row>
     <row r="18">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3645.64</v>
+        <v>3522.55</v>
       </c>
     </row>
   </sheetData>
